--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="179">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Dispositif médical usage</t>
+    <t>Entrée Dispositif médical usage</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -406,15 +406,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
   </si>
   <si>
     <t>fr-lm-device-use.status</t>
@@ -887,7 +878,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ30"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="true" bestFit="true"/>
@@ -2450,7 +2441,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2500,11 +2491,9 @@
       <c r="X16" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2522,10 +2511,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2565,13 +2554,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2600,9 +2589,11 @@
       <c r="X17" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y17" s="2"/>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2632,15 +2623,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2648,7 +2639,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2663,13 +2654,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2720,10 +2711,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2732,26 +2723,26 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2763,15 +2754,17 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -2808,50 +2801,50 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2863,16 +2856,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2910,39 +2903,39 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>136</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2950,7 +2943,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2965,17 +2958,15 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>156</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3024,10 +3015,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3036,15 +3027,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3067,13 +3058,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3124,7 +3115,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3136,15 +3127,15 @@
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>163</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3170,10 +3161,10 @@
         <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3224,7 +3215,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3241,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3270,10 +3261,10 @@
         <v>117</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3324,7 +3315,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3341,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3352,7 +3343,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3367,13 +3358,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3402,11 +3393,9 @@
       <c r="X25" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3424,10 +3413,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3441,10 +3430,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3467,13 +3456,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3502,9 +3491,11 @@
       <c r="X26" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y26" s="2"/>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3522,7 +3513,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3550,7 +3541,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3565,13 +3556,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3601,7 +3592,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3625,7 +3616,7 @@
         <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3653,7 +3644,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3665,13 +3656,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3701,7 +3692,7 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -3728,7 +3719,7 @@
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3753,7 +3744,7 @@
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3765,13 +3756,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>179</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3828,112 +3819,12 @@
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-device-use.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -1856,13 +1860,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1913,7 +1917,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1930,10 +1934,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1956,13 +1960,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2013,7 +2017,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2030,10 +2034,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2056,13 +2060,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2113,7 +2117,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2130,10 +2134,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2156,13 +2160,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2213,7 +2217,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2230,10 +2234,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2256,13 +2260,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2313,7 +2317,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2330,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2356,13 +2360,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2413,7 +2417,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2430,10 +2434,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2456,13 +2460,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2493,7 +2497,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2511,7 +2515,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2528,10 +2532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2554,13 +2558,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2611,7 +2615,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2623,15 +2627,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2654,13 +2658,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2711,7 +2715,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2728,14 +2732,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -2754,16 +2758,16 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2801,19 +2805,19 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2825,15 +2829,15 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2856,16 +2860,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2915,7 +2919,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2932,10 +2936,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2958,13 +2962,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3015,7 +3019,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3027,15 +3031,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3058,13 +3062,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3115,7 +3119,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3132,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3158,13 +3162,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3215,7 +3219,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3232,10 +3236,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3258,13 +3262,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3315,7 +3319,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3332,10 +3336,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3358,13 +3362,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3395,7 +3399,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3413,7 +3417,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3430,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3456,13 +3460,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3513,7 +3517,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3530,10 +3534,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3556,13 +3560,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3592,7 +3596,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3613,7 +3617,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3630,10 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3656,13 +3660,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3713,7 +3717,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3730,10 +3734,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3756,13 +3760,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3813,7 +3817,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-device-use.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-device-use.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-device-use.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-device-use.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-device-use.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-device-use.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-device-use.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-device-use.header.source</t>
+    <t>fr-lm-device-use.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-device-use.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -412,7 +454,7 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-device-use.status</t>
+    <t>fr-lm-device-use.usageStatus</t>
   </si>
   <si>
     <t>Status de l'utilisation du DM (ex active, completed, etc).</t>
@@ -545,10 +587,6 @@
   </si>
   <si>
     <t>fr-lm-device-use.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
-</t>
   </si>
   <si>
     <t>Dispositif médical</t>
@@ -882,11 +920,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.33203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.0390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.0390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -909,14 +947,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="31.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.94140625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.97265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1660,13 +1698,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1717,7 +1755,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1734,10 +1772,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1760,13 +1798,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1817,7 +1855,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1834,10 +1872,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1860,13 +1898,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1917,7 +1955,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1934,10 +1972,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1960,7 +1998,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2060,13 +2098,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2117,7 +2155,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2134,10 +2172,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2148,7 +2186,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2160,13 +2198,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2217,13 +2255,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2234,10 +2272,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2248,7 +2286,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2260,13 +2298,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2317,13 +2355,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2334,10 +2372,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2348,7 +2386,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2360,13 +2398,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2417,13 +2455,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2434,10 +2472,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2445,7 +2483,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2460,13 +2498,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2495,9 +2533,11 @@
       <c r="X16" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2515,10 +2555,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2532,10 +2572,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2558,13 +2598,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2594,10 +2634,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2615,7 +2655,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2627,15 +2667,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2658,13 +2698,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2715,7 +2755,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2732,21 +2772,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2758,17 +2798,15 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -2805,39 +2843,39 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2860,17 +2898,15 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2897,11 +2933,9 @@
       <c r="X20" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y20" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2919,7 +2953,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2936,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2947,7 +2981,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2962,13 +2996,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3019,10 +3053,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3031,15 +3065,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3062,13 +3096,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3119,7 +3153,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3136,21 +3170,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3162,15 +3196,17 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3207,39 +3243,39 @@
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3247,7 +3283,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3262,15 +3298,17 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3319,10 +3357,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3336,10 +3374,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3347,7 +3385,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3362,13 +3400,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3397,9 +3435,11 @@
       <c r="X25" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y25" s="2"/>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3417,10 +3457,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3429,15 +3469,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3445,7 +3485,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3460,13 +3500,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3517,10 +3557,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3534,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3560,13 +3600,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3596,7 +3636,7 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -3617,7 +3657,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3634,10 +3674,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3648,7 +3688,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3660,13 +3700,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3717,13 +3757,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3734,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3745,7 +3785,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>
@@ -3760,13 +3800,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3795,11 +3835,9 @@
       <c r="X29" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Y29" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>73</v>
@@ -3817,10 +3855,10 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -3829,6 +3867,406 @@
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -593,6 +593,10 @@
   </si>
   <si>
     <t>fr-lm-device-use.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>localisation anatomique</t>
@@ -3998,13 +4002,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>131</v>
+        <v>186</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4034,7 +4038,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4072,10 +4076,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4098,13 +4102,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4155,7 +4159,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4172,10 +4176,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4201,10 +4205,10 @@
         <v>150</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4255,7 +4259,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-device-use.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
